--- a/config/services模板.xlsx
+++ b/config/services模板.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
   <si>
     <t>service_name</t>
   </si>
@@ -67,178 +67,6 @@
   <si>
     <t>多条 Ingress YAML
 每条之间加一行 ---</t>
-  </si>
-  <si>
-    <t>file-kd</t>
-  </si>
-  <si>
-    <t>person-kd</t>
-  </si>
-  <si>
-    <t>cloud-test-default-group</t>
-  </si>
-  <si>
-    <t xml:space="preserve">apiVersion: apps/v1
-kind: Deployment
-metadata:
-  annotations:
-    deployment.kubernetes.io/revision: '164'
-    field.cattle.io/publicEndpoints: 'null'
-  labels:
-    app.name: yun-file-agent-kd
-    k8s.kuboard.cn/name: yun-file-agent-kd
-  name: yun-file-agent-kd
-  namespace: test
-spec:
-  progressDeadlineSeconds: 600
-  replicas: 1
-  revisionHistoryLimit: 10
-  selector:
-    matchLabels:
-      app.name: yun-file-agent-kd
-      sidecar.mesh.io/lane: mse-base
-  strategy:
-    rollingUpdate:
-      maxSurge: 25%
-      maxUnavailable: 25%
-    type: RollingUpdate
-  template:
-    metadata:
-      annotations:
-        cattle.io/timestamp: '2023-07-13T08:49:05Z'
-        kubectl.kubernetes.io/restartedAt: '2024-10-18T12:10:13+08:00'
-      creationTimestamp: null
-      labels:
-        app: yun-file-agent-kd
-        app.name: yun-file-agent-kd
-        sidecar.mesh.io/data-plane-mode: java_proxyless
-        sidecar.mesh.io/lane: mse-base
-        sidecar.mesh.io/mse-namespace: cloud-test-default-group
-    spec:
-      containers:
-      - env:
-        - name: ACTIVE_PROFILE
-          value: test
-        envFrom:
-        - configMapRef:
-            name: mse-publish-gray
-        - secretRef:
-            name: yun-file-agent-kd-secret
-        image: d133ypcgtest01-c138372f.ecis.guangzhou-2.cmecloud.cn/k8s/yun-file-agent-kd:release_1.7.0.202511141018
-        imagePullPolicy: Always
-        name: yun-file-agent-kd
-        resources:
-          limits:
-            cpu: '4'
-            memory: 8Gi
-          requests:
-            cpu: 100m
-            memory: 1Gi
-        terminationMessagePath: /dev/termination-log
-        terminationMessagePolicy: File
-        volumeMounts:
-        - mountPath: /logs
-          name: logs
-      dnsPolicy: ClusterFirst
-      imagePullSecrets:
-      - name: paas-d133ypcgtest01-harbor-secret
-      nodeSelector:
-        normal: 'true'
-      restartPolicy: Always
-      schedulerName: default-scheduler
-      securityContext: {}
-      terminationGracePeriodSeconds: 30
-      volumes:
-      - hostPath:
-          path: /var/lib/docker/logs
-          type: DirectoryOrCreate
-        name: logs
-</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kind: Service
-metadata:
-  annotations:
-    kubectl.kubernetes.io/last-applied-configuration: '{"apiVersion":"v1","kind":"Service","metadata":{"annotations":{"objectset.rio.cattle.io/applied":"H4sIAAAAAAAA/4SRzWobMRSF3+WsZ9yRLScz2pVAIZtiaOmmZHFHupOokSUh3QwYM+9eVEN3JktJ3/lB5wrK/heX6lOEwarQ4d1HB4MfXFZvGR3OLORICOYKijEJiU+xtmOa/7CVyrIrPu0siQTe+fTFN4fF7bU7HudeTwv3Wj9QT/tH1U/LTHtFgyZy2DoEmjn8s6Ocd5HODIPLR+wXH7inV47Svzt0d9PeqL7BQB+PszqMmvd0WA6Pg3KTnZi0tjSSHu08jJMdlGqZ91L6ulrcnmsm2xjHK4eUm6pmtq2nz9/o7IPnCvMbz6f1AS8dcirSLq733RuCGwkzDqPqkEuSZFOAwc+nEzoIlVeW039ke+lQObCVVD79pFaSa5vz67L46OUCg+8pth3lkpvoKXxU4fJ8wrb9DQAA///N7sU1AAIAAA","objectset.rio.cattle.io/id":"fd24d55b-49fe-446a-a271-9fba21a04aad"},"creationTimestamp":"2023-12-14T10:42:53Z","labels":{"app.name":"yun-file-agent-kd","objectset.rio.cattle.io/hash":"455b1384e2a3f3701d9c9ea44ca8a48cb089c011"},"name":"yun-file-agent-kd-svc","namespace":"test","resourceVersion":"1201524211","uid":"4e3c5e73-aa32-4cd7-bf38-bc69449ab5e4"},"spec":{"ipFamilies":["IPv6"],"ipFamilyPolicy":"SingleStack","ports":[{"name":"yun-file-agent-kd-port","port":8081,"protocol":"TCP","targetPort":8081}],"selector":{"app.name":"yun-file-agent-kd"},"sessionAffinity":"None","type":"ClusterIP"},"status":{"loadBalancer":{}}}
-      '
-    objectset.rio.cattle.io/applied: H4sIAAAAAAAA/4SRzWobMRSF3+WsZ9yRLScz2pVAIZtiaOmmZHFHupOokSUh3QwYM+9eVEN3JktJ3/lB5wrK/heX6lOEwarQ4d1HB4MfXFZvGR3OLORICOYKijEJiU+xtmOa/7CVyrIrPu0siQTe+fTFN4fF7bU7HudeTwv3Wj9QT/tH1U/LTHtFgyZy2DoEmjn8s6Ocd5HODIPLR+wXH7inV47Svzt0d9PeqL7BQB+PszqMmvd0WA6Pg3KTnZi0tjSSHu08jJMdlGqZ91L6ulrcnmsm2xjHK4eUm6pmtq2nz9/o7IPnCvMbz6f1AS8dcirSLq733RuCGwkzDqPqkEuSZFOAwc+nEzoIlVeW039ke+lQObCVVD79pFaSa5vz67L46OUCg+8pth3lkpvoKXxU4fJ8wrb9DQAA///N7sU1AAIAAA
-    objectset.rio.cattle.io/id: fd24d55b-49fe-446a-a271-9fba21a04aad
-  labels:
-    app.name: yun-file-agent-kd
-    objectset.rio.cattle.io/hash: 455b1384e2a3f3701d9c9ea44ca8a48cb089c011
-  name: yun-file-agent-kd-svc
-  namespace: test
-spec:
-  clusterIP: fd11:1111:1111:15::f65d
-  clusterIPs:
-  - fd11:1111:1111:15::f65d
-  ipFamilies:
-  - IPv6
-  ipFamilyPolicy: SingleStack
-  ports:
-  - name: yun-file-agent-kd-port
-    port: 8081
-    protocol: TCP
-    targetPort: 8081
-  selector:
-    app.name: yun-file-agent-kd
-    sidecar.mesh.io/lane: mse-base
-  sessionAffinity: None
-  type: ClusterIP
-</t>
-  </si>
-  <si>
-    <t>apiVersion: networking.k8s.io/v1
-kind: Ingress
-metadata:
-  annotations:
-    k8s.apisix.apache.org/enable-lane: 'false'
-    objectset.rio.cattle.io/applied: H4sIAAAAAAAA/3SQMe+bMBTEv8vNmJBAEsPaqUvVoepSdXiYR3BDbMt+Sf8R4rtXDv+xkbz49O53p1tAwf7kmKx36OBY/vp4te5SXnUqrd899ihwtW5Ah6/uEjklFLix0EBC6BaQc15IrHcpf33/h40kljJaXxoSmTmDbCbs9aDrw7lX1Iy1akzdKzqPpNpjPVTmrI/V4YC1wEw9zy8chVA6ujE6PO9OjXZmRRd2osKQm7yLmyhN6NCO+7FqdVONp4M2mvXx1A7DYOqWTmNtmlbrc3PSxxz6GbPRrcOmpEAmy8JJ8lUKbHIxu43xZaaUvn06g032AwXifeaE7teCySf5b/XyGcxFZWhp/A0FJpGQuYFk2rw9mSvn4Rckjg+bayx4O4ZKD4MCwUd53d1vPUd0utL7dV2LFxgddtm1e7mwiT+eIRO/Rx7tB9bfa37/AgAA//+NNQadGQIAAA
-    objectset.rio.cattle.io/id: 18d8327b-a4f3-4c3b-a7fa-953d0c785022
-  labels:
-    app.name: yun-file-agent-pds
-    objectset.rio.cattle.io/hash: 9f1f09840f628c8e8569dddc39a6f3c498874685
-  name: agent-in-a
-  namespace: test
-spec:
-  ingressClassName: apisix
-  rules:
-  - host: yun-file-agent-pds.ypcg-test.com
-    http:
-      paths:
-      - backend:
-          service:
-            name: yun-file-agent-pds-svc-a
-            port:
-              number: 8081
-        path: /file/agent
-        pathType: Prefix
----
-apiVersion: networking.k8s.io/v1
-kind: Ingress
-metadata:
-  annotations:
-    k8s.apisix.apache.org/enable-lane: 'false'
-    objectset.rio.cattle.io/applied: H4sIAAAAAAAA/3SQMe+bMBTEv8vNmJBAEsPaqUvVoepSdXiYR3BDbMt+Sf8R4rtXDv+xkbz49O53p1tAwf7kmKx36OBY/vp4te5SXnUqrd899ihwtW5Ah6/uEjklFLix0EBC6BaQc15IrHcpf33/h40kljJaXxoSmTmDbCbs9aDrw7lX1Iy1akzdKzqPpNpjPVTmrI/V4YC1wEw9zy8chVA6ujE6PO9OjXZmRRd2osKQm7yLmyhN6NCO+7FqdVONp4M2mvXx1A7DYOqWTmNtmlbrc3PSxxz6GbPRrcOmpEAmy8JJ8lUKbHIxu43xZaaUvn06g032AwXifeaE7teCySf5b/XyGcxFZWhp/A0FJpGQuYFk2rw9mSvn4Rckjg+bayx4O4ZKD4MCwUd53d1vPUd0utL7dV2LFxgddtm1e7mwiT+eIRO/Rx7tB9bfa37/AgAA//+NNQadGQIAAA
-    objectset.rio.cattle.io/id: 18d8327b-a4f3-4c3b-a7fa-953d0c785022
-  labels:
-    app.name: yun-file-agent-pds
-    objectset.rio.cattle.io/hash: 9f1f09840f628c8e8569dddc39a6f3c498874685
-  name: agent-in
-  namespace: test
-spec:
-  ingressClassName: apisix
-  rules:
-  - host: yun-file-agent-pds.ypcg-test.com
-    http:
-      paths:
-      - backend:
-          service:
-            name: yun-file-agent-pds-svc
-            port:
-              number: 8081
-        path: /file/agent
-        pathType: Prefix</t>
   </si>
 </sst>
 </file>
@@ -1271,24 +1099,12 @@
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:6">
-      <c r="A3" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>17</v>
-      </c>
+      <c r="A3" s="3"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
     </row>
     <row r="4" ht="17" spans="1:6">
       <c r="A4" s="3"/>
